--- a/output/pdf_financials_xlsx/ATOM.xlsx
+++ b/output/pdf_financials_xlsx/ATOM.xlsx
@@ -6020,49 +6020,49 @@
         <v>0.040742</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.040742</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.040742</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.040742</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.040742</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.040742</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.236742</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.236742</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.236742</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.496642</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.500642</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.746852</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.900595</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.914636</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.162034</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.183057</v>
       </c>
     </row>
     <row r="93">
@@ -10060,7 +10060,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -12004,7 +12008,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13111,7 +13119,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13707,7 +13719,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATOM.xlsx
+++ b/output/pdf_financials_xlsx/ATOM.xlsx
@@ -2550,55 +2550,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.942446</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.120578</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.926482</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.7513879999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.481408</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.192512</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004514</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.034843</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.008031</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.064481</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.029644</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.249282</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.604822</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.004158</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000552</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.013986</v>
       </c>
     </row>
     <row r="35">
@@ -2666,55 +2666,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.942446</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.120578</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.926482</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.7513879999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.481408</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.192512</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004514</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.034843</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.008031</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.064481</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.029644</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.249282</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.604822</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.004158</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000552</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.013986</v>
       </c>
     </row>
     <row r="37">
@@ -3362,55 +3362,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.961426</v>
+        <v>0.01898</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.171154</v>
+        <v>0.050576</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.082062</v>
+        <v>0.15558</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.795739</v>
+        <v>0.044351</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.486097</v>
+        <v>0.004689</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.205934</v>
+        <v>0.013422</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.012252</v>
+        <v>0.007738</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.055761</v>
+        <v>0.020918</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.035098</v>
+        <v>0.027067</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.03417</v>
+        <v>0.03107</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.112201</v>
+        <v>0.04772</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.029644</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.271758</v>
+        <v>0.022476</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.729768</v>
+        <v>0.124946</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.032419</v>
+        <v>0.028261</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.038857</v>
+        <v>0.038305</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.019055</v>
+        <v>0.005069</v>
       </c>
     </row>
     <row r="49">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
